--- a/src/nodes/HPC/compressor_stage_8_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_8_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-13.911392007448722</v>
+        <v>-13.909018522030392</v>
       </c>
       <c r="B1">
-        <v>5.1894838169559288</v>
+        <v>5.1958419553688513</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-12.833970795297205</v>
+        <v>-12.850559019638288</v>
       </c>
       <c r="B2">
-        <v>5.6196957490679642</v>
+        <v>5.5808952729819676</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-11.936848824843379</v>
+        <v>-11.960681944090402</v>
       </c>
       <c r="B3">
-        <v>5.6290216795751453</v>
+        <v>5.5729104566481258</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-11.066402988305327</v>
+        <v>-11.095852534377839</v>
       </c>
       <c r="B4">
-        <v>5.57607551599936</v>
+        <v>5.50652875978569</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-10.214095746619252</v>
+        <v>-10.248093712028966</v>
       </c>
       <c r="B5">
-        <v>5.4807870741638594</v>
+        <v>5.4003481827647475</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-9.3764472353317458</v>
+        <v>-9.41415394285534</v>
       </c>
       <c r="B6">
-        <v>5.3512796618659086</v>
+        <v>5.2619494500642014</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-8.5514718313657738</v>
+        <v>-8.5921778209471817</v>
       </c>
       <c r="B7">
-        <v>5.1921884675273393</v>
+        <v>5.0956583107561437</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-7.73800268345037</v>
+        <v>-7.7810749502851717</v>
       </c>
       <c r="B8">
-        <v>5.0062373593202354</v>
+        <v>4.9040169468741395</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-6.9342146272534118</v>
+        <v>-6.9791398704610081</v>
       </c>
       <c r="B9">
-        <v>4.7976869548200289</v>
+        <v>4.6910015200439634</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-6.1381369337371767</v>
+        <v>-6.18453112385959</v>
       </c>
       <c r="B10">
-        <v>4.5711376741789369</v>
+        <v>4.4609052598645214</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-5.3478749281026143</v>
+        <v>-5.3954783284275445</v>
       </c>
       <c r="B11">
-        <v>4.3310123984529429</v>
+        <v>4.2178556882350762</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-4.562417689195315</v>
+        <v>-4.61103682671412</v>
       </c>
       <c r="B12">
-        <v>4.079670996483487</v>
+        <v>3.964055207912617</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-3.7842132562007507</v>
+        <v>-3.8334937841173122</v>
       </c>
       <c r="B13">
-        <v>3.8113988273500423</v>
+        <v>3.6941714527847132</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-3.014726090262247</v>
+        <v>-3.0642173885044413</v>
       </c>
       <c r="B14">
-        <v>3.5227772899020122</v>
+        <v>3.405014588558867</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.2480273800146522</v>
+        <v>-2.2976680947713808</v>
       </c>
       <c r="B15">
-        <v>3.2276464518304842</v>
+        <v>3.1094996770917489</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.4786792487239111</v>
+        <v>-1.5287650593662761</v>
       </c>
       <c r="B16">
-        <v>2.938700355408</v>
+        <v>2.8194723496622549</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-0.71060083068880864</v>
+        <v>-0.7611699779177844</v>
       </c>
       <c r="B17">
-        <v>2.6467902723912267</v>
+        <v>2.5263956190890253</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>0.051147169609218029</v>
+        <v>0.00038884243645548495</v>
       </c>
       <c r="B18">
-        <v>2.3401026218996357</v>
+        <v>2.2192457680790274</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.80629477799101124</v>
+        <v>0.75565918770343277</v>
       </c>
       <c r="B19">
-        <v>2.0180071830197566</v>
+        <v>1.8974347773527764</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.5557697028529929</v>
+        <v>1.5055078671763054</v>
       </c>
       <c r="B20">
-        <v>1.6826695748298799</v>
+        <v>1.5629835521341746</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.3004996525915713</v>
+        <v>2.2508016901482164</v>
       </c>
       <c r="B21">
-        <v>1.3362554164083025</v>
+        <v>1.2179129976471257</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.0412472011385288</v>
+        <v>2.9922531680161355</v>
       </c>
       <c r="B22">
-        <v>0.98054484110473039</v>
+        <v>0.8638842843654464</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>3.7781143845670844</v>
+        <v>3.7299576205922729</v>
       </c>
       <c r="B23">
-        <v>0.61577603935453973</v>
+        <v>0.50111964376261853</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>4.5110381044858165</v>
+        <v>4.4638560697926515</v>
       </c>
       <c r="B24">
-        <v>0.24180171586452243</v>
+        <v>0.12948157256203866</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>5.2399552625033161</v>
+        <v>5.1938895375333036</v>
       </c>
       <c r="B25">
-        <v>-0.14152542465853402</v>
+        <v>-0.2511674325128988</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>5.9647755386589836</v>
+        <v>5.9199736041484732</v>
       </c>
       <c r="B26">
-        <v>-0.5344162228522269</v>
+        <v>-0.641024190006777</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>6.6852997267155354</v>
+        <v>6.641922083645321</v>
       </c>
       <c r="B27">
-        <v>-0.937335700731729</v>
+        <v>-1.0405227795361136</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>7.4013013988665026</v>
+        <v>7.3595233484492208</v>
       </c>
       <c r="B28">
-        <v>-1.3508124256565985</v>
+        <v>-1.450156595985401</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>8.1125541273054242</v>
+        <v>8.0725657709855554</v>
       </c>
       <c r="B29">
-        <v>-1.7753749649863972</v>
+        <v>-1.870419034239138</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>8.8189544864867155</v>
+        <v>8.7809526404873139</v>
       </c>
       <c r="B30">
-        <v>-2.2112647527057336</v>
+        <v>-2.3015355686845944</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>9.5208910599083</v>
+        <v>9.4850469134179356</v>
       </c>
       <c r="B31">
-        <v>-2.6575746892994139</v>
+        <v>-2.7426599917201382</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>10.218875433328995</v>
+        <v>10.185326463048494</v>
       </c>
       <c r="B32">
-        <v>-3.1131105418773006</v>
+        <v>-3.1926781752469235</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>10.913419192507606</v>
+        <v>10.882269162650038</v>
       </c>
       <c r="B33">
-        <v>-3.5766780775492464</v>
+        <v>-3.6504759911660956</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>11.604835132751775</v>
+        <v>11.576167141619948</v>
       </c>
       <c r="B34">
-        <v>-4.0475471148396469</v>
+        <v>-4.1153723602254031</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>12.292640887564462</v>
+        <v>12.266569553860894</v>
       </c>
       <c r="B35">
-        <v>-4.5268436779310521</v>
+        <v>-4.5884183985590088</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>12.976155299997453</v>
+        <v>12.952839809401866</v>
       </c>
       <c r="B36">
-        <v>-5.0161578424205437</v>
+        <v>-5.0710982711476742</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>13.654697213102551</v>
+        <v>13.63434131827186</v>
       </c>
       <c r="B37">
-        <v>-5.5170796839052132</v>
+        <v>-5.56489614297217</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>14.327097974583504</v>
+        <v>14.309982001980306</v>
       </c>
       <c r="B38">
-        <v>-6.0323372748250854</v>
+        <v>-6.07235811863006</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>14.990238950751929</v>
+        <v>14.976847827958391</v>
       </c>
       <c r="B39">
-        <v>-6.5692106749919352</v>
+        <v>-6.600278061186108</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>15.640514012571384</v>
+        <v>15.631569275117746</v>
       </c>
       <c r="B40">
-        <v>-7.1361179410604754</v>
+        <v>-7.1565117733218795</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>16.274317031005449</v>
+        <v>16.270776822370003</v>
       </c>
       <c r="B41">
-        <v>-7.74147712968542</v>
+        <v>-7.748915057718941</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>16.274317031005449</v>
+        <v>16.270776822370003</v>
       </c>
       <c r="B42">
-        <v>-7.74147712968542</v>
+        <v>-7.748915057718941</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>15.47025680191536</v>
+        <v>15.472493007284403</v>
       </c>
       <c r="B43">
-        <v>-7.533562078721129</v>
+        <v>-7.5273869625979213</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>14.678964858844379</v>
+        <v>14.686015383193945</v>
       </c>
       <c r="B44">
-        <v>-7.2958410629656019</v>
+        <v>-7.2783335591478187</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>13.896841358877504</v>
+        <v>13.907980721838372</v>
       </c>
       <c r="B45">
-        <v>-7.03671746491024</v>
+        <v>-7.0095959787617046</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>13.120286459099757</v>
+        <v>13.135025794957429</v>
       </c>
       <c r="B46">
-        <v>-6.7645946670464472</v>
+        <v>-6.7290153528326577</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>12.346187589411414</v>
+        <v>12.364242640040226</v>
       </c>
       <c r="B47">
-        <v>-6.486738574497573</v>
+        <v>-6.4433713925100626</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>11.573381270973824</v>
+        <v>11.594544357573367</v>
       </c>
       <c r="B48">
-        <v>-6.2058651829147458</v>
+        <v>-6.1551981279685606</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>10.801191297763593</v>
+        <v>10.825299313792806</v>
       </c>
       <c r="B49">
-        <v>-5.923553010581033</v>
+        <v>-5.8659681691390944</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>10.028941463757338</v>
+        <v>10.055875874934513</v>
       </c>
       <c r="B50">
-        <v>-5.641380575779511</v>
+        <v>-5.5771541259526174</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>9.2561541085837646</v>
+        <v>9.285827906047869</v>
       </c>
       <c r="B51">
-        <v>-5.3604629168315165</v>
+        <v>-5.2897961308343229</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>8.4831457544799189</v>
+        <v>8.5154512674359353</v>
       </c>
       <c r="B52">
-        <v>-5.0800611522114458</v>
+        <v>-5.0032044061863941</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>7.7104314693349441</v>
+        <v>7.7452273182151927</v>
       </c>
       <c r="B53">
-        <v>-4.7989729204319636</v>
+        <v>-4.7162566969052628</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>6.9385263210379637</v>
+        <v>6.9756374175021065</v>
       </c>
       <c r="B54">
-        <v>-4.5159958600057273</v>
+        <v>-4.4278307478873513</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>6.1678221419123549</v>
+        <v>6.2070477740517447</v>
       </c>
       <c r="B55">
-        <v>-4.2302152874413936</v>
+        <v>-4.1370727690406621</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>5.3982178220184283</v>
+        <v>5.4393639951735206</v>
       </c>
       <c r="B56">
-        <v>-3.941867231231591</v>
+        <v>-3.844202830319476</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4.6294890158507194</v>
+        <v>4.6723765378154249</v>
       </c>
       <c r="B57">
-        <v>-3.651475397864937</v>
+        <v>-3.5497094666896416</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3.8614113779037758</v>
+        <v>3.9058758589254579</v>
       </c>
       <c r="B58">
-        <v>-3.3595634938300551</v>
+        <v>-3.2540812131170131</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3.0937875541672311</v>
+        <v>3.13967762671384</v>
       </c>
       <c r="B59">
-        <v>-3.0665922173502893</v>
+        <v>-2.9577478262733541</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2.3265281566111269</v>
+        <v>2.3736983544397368</v>
       </c>
       <c r="B60">
-        <v>-2.7727702335878965</v>
+        <v>-2.6609039496541058</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.5595707887005921</v>
+        <v>1.6078797666245304</v>
       </c>
       <c r="B61">
-        <v>-2.4782431994398539</v>
+        <v>-2.3636854484606191</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.79285305390076344</v>
+        <v>0.84216358778961353</v>
       </c>
       <c r="B62">
-        <v>-2.1831567718031453</v>
+        <v>-2.0662281878942488</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.02647745162370058</v>
+        <v>0.076645601580375</v>
       </c>
       <c r="B63">
-        <v>-1.8872716786359083</v>
+        <v>-1.7683088550869262</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.738793934930857</v>
+        <v>-0.68796217186182207</v>
       </c>
       <c r="B64">
-        <v>-1.5888089321409034</v>
+        <v>-1.4682674248928767</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.5020341266162347</v>
+        <v>-1.4507936532716057</v>
       </c>
       <c r="B65">
-        <v>-1.2856046155820529</v>
+        <v>-1.1640846940969072</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.2623161442857707</v>
+        <v>-2.2109827633836168</v>
       </c>
       <c r="B66">
-        <v>-0.97549481222327372</v>
+        <v>-0.85374145948381841</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.0199108833686612</v>
+        <v>-2.9687826384237876</v>
       </c>
       <c r="B67">
-        <v>-0.65911189352090371</v>
+        <v>-0.53782789045464774</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-3.7798807375975736</v>
+        <v>-3.7289232765832514</v>
       </c>
       <c r="B68">
-        <v>-0.3482733837009504</v>
+        <v>-0.22737164687536282</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-4.5461468079674949</v>
+        <v>-4.4950683422851405</v>
       </c>
       <c r="B69">
-        <v>-0.0521326020127221</v>
+        <v>0.069085693966124129</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-5.3132735262191968</v>
+        <v>-5.2621393029153438</v>
       </c>
       <c r="B70">
-        <v>0.24199910497091404</v>
+        <v>0.36338437555903247</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-6.0753346003206783</v>
+        <v>-6.0245991353907655</v>
       </c>
       <c r="B71">
-        <v>0.54795592387329117</v>
+        <v>0.66843357984444107</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-6.8337975124030645</v>
+        <v>-6.7838190517896253</v>
       </c>
       <c r="B72">
-        <v>0.86231220142609855</v>
+        <v>0.98103642179372064</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-7.5911135643168208</v>
+        <v>-7.5420894836558512</v>
       </c>
       <c r="B73">
-        <v>1.1793456804259526</v>
+        <v>1.29585292050369</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-8.346275562626646</v>
+        <v>-8.298469505234916</v>
       </c>
       <c r="B74">
-        <v>1.5014075278208336</v>
+        <v>1.6150767785426754</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-9.0973927954346685</v>
+        <v>-9.0511927016026466</v>
       </c>
       <c r="B75">
-        <v>1.832911373770201</v>
+        <v>1.9428262687257576</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-9.8424989722784471</v>
+        <v>-9.7984220584547543</v>
       </c>
       <c r="B76">
-        <v>2.1784472771280754</v>
+        <v>2.2833842613835365</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-10.579773611185182</v>
+        <v>-10.538456802737866</v>
       </c>
       <c r="B77">
-        <v>2.5422649250884475</v>
+        <v>2.6407159899017145</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-11.30805504270511</v>
+        <v>-11.27021172578238</v>
       </c>
       <c r="B78">
-        <v>2.9270760895106371</v>
+        <v>3.0173515423708936</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-12.025363052108251</v>
+        <v>-11.991836835795724</v>
       </c>
       <c r="B79">
-        <v>3.3375033337075992</v>
+        <v>3.4176040452276717</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-12.72822363477783</v>
+        <v>-12.700086464677977</v>
       </c>
       <c r="B80">
-        <v>3.7816562864217511</v>
+        <v>3.8490405465759765</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-13.408105461328082</v>
+        <v>-13.386989750260646</v>
       </c>
       <c r="B81">
-        <v>4.2794502677605992</v>
+        <v>4.3302445539100152</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-13.911392007448722</v>
+        <v>-13.909018522030392</v>
       </c>
       <c r="B82">
-        <v>5.1894838169559288</v>
+        <v>5.1958419553688513</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-16.497791928699954</v>
+        <v>-16.498168440314085</v>
       </c>
       <c r="B1">
-        <v>4.7511465058761777</v>
+        <v>4.7498389191635875</v>
       </c>
       <c r="C1">
         <v>215.66601106843655</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-15.467768952256041</v>
+        <v>-15.49753159770091</v>
       </c>
       <c r="B2">
-        <v>4.8555912718912984</v>
+        <v>4.761906344580817</v>
       </c>
       <c r="C2">
         <v>215.66601106843655</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-14.504864683199482</v>
+        <v>-14.545734816309414</v>
       </c>
       <c r="B3">
-        <v>4.7488557551286048</v>
+        <v>4.6202626675672729</v>
       </c>
       <c r="C3">
         <v>215.66601106843655</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-13.552103784632438</v>
+        <v>-13.601538088642519</v>
       </c>
       <c r="B4">
-        <v>4.6102054424516687</v>
+        <v>4.4546998428843789</v>
       </c>
       <c r="C4">
         <v>215.66601106843655</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-12.606320475271645</v>
+        <v>-12.662649818504569</v>
       </c>
       <c r="B5">
-        <v>4.4496010529004533</v>
+        <v>4.2724300600492811</v>
       </c>
       <c r="C5">
         <v>215.66601106843655</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-11.666224736524876</v>
+        <v>-11.728136130994974</v>
       </c>
       <c r="B6">
-        <v>4.2711014621848822</v>
+        <v>4.0763924419236828</v>
       </c>
       <c r="C6">
         <v>215.66601106843655</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-10.731080689561704</v>
+        <v>-10.797464258443737</v>
       </c>
       <c r="B7">
-        <v>4.0770220173303828</v>
+        <v>3.8682637330456644</v>
       </c>
       <c r="C7">
         <v>215.66601106843655</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-9.80045609953948</v>
+        <v>-9.8703212216949971</v>
       </c>
       <c r="B8">
-        <v>3.8687226890492825</v>
+        <v>3.6490289520634995</v>
       </c>
       <c r="C8">
         <v>215.66601106843655</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-8.8736745234761543</v>
+        <v>-8.946217290250905</v>
       </c>
       <c r="B9">
-        <v>3.648331817200825</v>
+        <v>3.420229395462806</v>
       </c>
       <c r="C9">
         <v>215.66601106843655</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-7.9500055058893384</v>
+        <v>-8.0246236438353318</v>
       </c>
       <c r="B10">
-        <v>3.4181476849512413</v>
+        <v>3.1835293844094132</v>
       </c>
       <c r="C10">
         <v>215.66601106843655</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-7.0287467494347142</v>
+        <v>-7.1050318544010036</v>
       </c>
       <c r="B11">
-        <v>3.180379979547785</v>
+        <v>2.9405290609526542</v>
       </c>
       <c r="C11">
         <v>215.66601106843655</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-6.109523700735652</v>
+        <v>-6.187170726726233</v>
       </c>
       <c r="B12">
-        <v>2.9362071844725124</v>
+        <v>2.6920819399214846</v>
       </c>
       <c r="C12">
         <v>215.66601106843655</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-5.1932446241481545</v>
+        <v>-5.2716976046627995</v>
       </c>
       <c r="B13">
-        <v>2.6827715640656669</v>
+        <v>2.4361192063798445</v>
       </c>
       <c r="C13">
         <v>215.66601106843655</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-4.2804529681491017</v>
+        <v>-4.3590057767845272</v>
       </c>
       <c r="B14">
-        <v>2.4183632283801679</v>
+        <v>2.1714030891468008</v>
       </c>
       <c r="C14">
         <v>215.66601106843655</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-3.368950099966237</v>
+        <v>-3.4475037714799144</v>
       </c>
       <c r="B15">
-        <v>2.1498998894614658</v>
+        <v>1.9029423218269208</v>
       </c>
       <c r="C15">
         <v>215.66601106843655</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.4567194440639244</v>
+        <v>-2.5357318985699608</v>
       </c>
       <c r="B16">
-        <v>1.8837264399399027</v>
+        <v>1.6353308910166648</v>
       </c>
       <c r="C16">
         <v>215.66601106843655</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.545214735102082</v>
+        <v>-1.6247423537909267</v>
       </c>
       <c r="B17">
-        <v>1.6152688927928358</v>
+        <v>1.3652572904945282</v>
       </c>
       <c r="C17">
         <v>215.66601106843655</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.63631306718992</v>
+        <v>-0.715893775115377</v>
       </c>
       <c r="B18">
-        <v>1.338621215556085</v>
+        <v>1.0884455686064114</v>
       </c>
       <c r="C18">
         <v>215.66601106843655</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.26988533796175918</v>
+        <v>0.19074131645419232</v>
       </c>
       <c r="B19">
-        <v>1.053468073652291</v>
+        <v>0.80466748478578753</v>
       </c>
       <c r="C19">
         <v>215.66601106843655</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.1737244767417694</v>
+        <v>1.0954119291578164</v>
       </c>
       <c r="B20">
-        <v>0.76089180697579539</v>
+        <v>0.51470672623801828</v>
       </c>
       <c r="C20">
         <v>215.66601106843655</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.0755483455389019</v>
+        <v>1.9983670712355079</v>
       </c>
       <c r="B21">
-        <v>0.46197475542094724</v>
+        <v>0.2193469801684729</v>
       </c>
       <c r="C21">
         <v>215.66601106843655</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>2.9756397194990396</v>
+        <v>2.8998114322522426</v>
       </c>
       <c r="B22">
-        <v>0.15760663420415244</v>
+        <v>-0.0807675474595493</v>
       </c>
       <c r="C22">
         <v>215.66601106843655</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>3.8740364887963357</v>
+        <v>3.7997724270727478</v>
       </c>
       <c r="B23">
-        <v>-0.152093340169919</v>
+        <v>-0.38555057565099465</v>
       </c>
       <c r="C23">
         <v>215.66601106843655</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>4.7707153223620145</v>
+        <v>4.6982331518866944</v>
       </c>
       <c r="B24">
-        <v>-0.46719857587453378</v>
+        <v>-0.695055304652872</v>
       </c>
       <c r="C24">
         <v>215.66601106843655</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>5.665652889127303</v>
+        <v>5.5951767028837534</v>
       </c>
       <c r="B25">
-        <v>-0.78778248108295912</v>
+        <v>-1.0093349347121909</v>
       </c>
       <c r="C25">
         <v>215.66601106843655</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>6.558815785355395</v>
+        <v>6.490578880121566</v>
       </c>
       <c r="B26">
-        <v>-1.1139501563082717</v>
+        <v>-1.3284656287109189</v>
       </c>
       <c r="C26">
         <v>215.66601106843655</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>7.4501303166373889</v>
+        <v>7.3843862991296785</v>
       </c>
       <c r="B27">
-        <v>-1.4459334714227994</v>
+        <v>-1.6526154000708682</v>
       </c>
       <c r="C27">
         <v>215.66601106843655</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>8.339512715896344</v>
+        <v>8.2765382793056</v>
       </c>
       <c r="B28">
-        <v>-1.7839959886386776</v>
+        <v>-1.9819752248488058</v>
       </c>
       <c r="C28">
         <v>215.66601106843655</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>9.22687921605533</v>
+        <v>9.1669741400468467</v>
       </c>
       <c r="B29">
-        <v>-2.128401270168045</v>
+        <v>-2.3167360791015037</v>
       </c>
       <c r="C29">
         <v>215.66601106843655</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>10.11219169312168</v>
+        <v>10.055666232728484</v>
       </c>
       <c r="B30">
-        <v>-2.4792692681950843</v>
+        <v>-2.6569849795220573</v>
       </c>
       <c r="C30">
         <v>215.66601106843655</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>10.995594595439824</v>
+        <v>10.942719036635825</v>
       </c>
       <c r="B31">
-        <v>-2.8361454947921758</v>
+        <v>-3.002393105348891</v>
       </c>
       <c r="C31">
         <v>215.66601106843655</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>11.877278014438488</v>
+        <v>11.828270063031745</v>
       </c>
       <c r="B32">
-        <v>-3.1984318520037531</v>
+        <v>-3.3525276764567575</v>
       </c>
       <c r="C32">
         <v>215.66601106843655</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>12.757432041546378</v>
+        <v>12.712456823179114</v>
       </c>
       <c r="B33">
-        <v>-3.5655302418742432</v>
+        <v>-3.7069559127204097</v>
       </c>
       <c r="C33">
         <v>215.66601106843655</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>13.636173065668517</v>
+        <v>13.595363475457281</v>
       </c>
       <c r="B34">
-        <v>-3.9370744618524802</v>
+        <v>-4.0654129480249</v>
       </c>
       <c r="C34">
         <v>215.66601106843655</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>14.513322665615211</v>
+        <v>14.476860766711559</v>
       </c>
       <c r="B35">
-        <v>-4.31362589100493</v>
+        <v>-4.42830557229648</v>
       </c>
       <c r="C35">
         <v>215.66601106843655</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>15.388628717673063</v>
+        <v>15.356766090903706</v>
       </c>
       <c r="B36">
-        <v>-4.6959778038024558</v>
+        <v>-4.7962084894717</v>
       </c>
       <c r="C36">
         <v>215.66601106843655</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>16.261839098128689</v>
+        <v>16.234896841995507</v>
       </c>
       <c r="B37">
-        <v>-5.0849234747159278</v>
+        <v>-5.1696964034871113</v>
       </c>
       <c r="C37">
         <v>215.66601106843655</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>17.132520903352553</v>
+        <v>17.110939556951994</v>
       </c>
       <c r="B38">
-        <v>-5.4818249787086559</v>
+        <v>-5.5497558558717932</v>
       </c>
       <c r="C38">
         <v>215.66601106843655</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>17.999518110050506</v>
+        <v>17.984057344751157</v>
       </c>
       <c r="B39">
-        <v>-5.8903195927137064</v>
+        <v>-5.9390207385249134</v>
       </c>
       <c r="C39">
         <v>215.66601106843655</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>18.861493915012218</v>
+        <v>18.853282457374217</v>
       </c>
       <c r="B40">
-        <v>-6.3146133941565825</v>
+        <v>-6.340536780938165</v>
       </c>
       <c r="C40">
         <v>215.66601106843655</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>19.717111515027398</v>
+        <v>19.717647146802431</v>
       </c>
       <c r="B41">
-        <v>-6.7589124604627973</v>
+        <v>-6.7573497126032462</v>
       </c>
       <c r="C41">
         <v>215.66601106843655</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>19.717111515027398</v>
+        <v>19.717647146802431</v>
       </c>
       <c r="B42">
-        <v>-6.7589124604627973</v>
+        <v>-6.7573497126032462</v>
       </c>
       <c r="C42">
         <v>215.66601106843655</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>18.798348616486013</v>
+        <v>18.807576662021116</v>
       </c>
       <c r="B43">
-        <v>-6.5132918627673417</v>
+        <v>-6.4843836151858207</v>
       </c>
       <c r="C43">
         <v>215.66601106843655</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>17.88407221861813</v>
+        <v>17.900495362920083</v>
       </c>
       <c r="B44">
-        <v>-6.25355507425429</v>
+        <v>-6.2020098508901889</v>
       </c>
       <c r="C44">
         <v>215.66601106843655</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>16.9729465608801</v>
+        <v>16.995436543887216</v>
       </c>
       <c r="B45">
-        <v>-5.98390489173402</v>
+        <v>-5.9132708685102875</v>
       </c>
       <c r="C45">
         <v>215.66601106843655</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>16.063635882728331</v>
+        <v>16.091433499310451</v>
       </c>
       <c r="B46">
-        <v>-5.7085441120169138</v>
+        <v>-5.621209116840058</v>
       </c>
       <c r="C46">
         <v>215.66601106843655</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>15.154985167461307</v>
+        <v>15.187650344509402</v>
       </c>
       <c r="B47">
-        <v>-5.43110684492324</v>
+        <v>-5.3284553205861043</v>
       </c>
       <c r="C47">
         <v>215.66601106843655</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>14.246562373745883</v>
+        <v>14.283774478530456</v>
       </c>
       <c r="B48">
-        <v>-5.1529524523128112</v>
+        <v>-5.0359933081056694</v>
       </c>
       <c r="C48">
         <v>215.66601106843655</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>13.33811620409103</v>
+        <v>13.3796241213517</v>
       </c>
       <c r="B49">
-        <v>-4.8748716090553215</v>
+        <v>-4.7443951836686553</v>
       </c>
       <c r="C49">
         <v>215.66601106843655</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>12.429395361005716</v>
+        <v>12.475017492951237</v>
       </c>
       <c r="B50">
-        <v>-4.5976549900204731</v>
+        <v>-4.4542330515449713</v>
       </c>
       <c r="C50">
         <v>215.66601106843655</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>11.520222209199213</v>
+        <v>11.569826125877343</v>
       </c>
       <c r="B51">
-        <v>-4.3218615015458175</v>
+        <v>-4.1659112288696818</v>
       </c>
       <c r="C51">
         <v>215.66601106843655</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>10.610713762182014</v>
+        <v>10.664134802959083</v>
       </c>
       <c r="B52">
-        <v>-4.0471229758403373</v>
+        <v>-3.8791628842384824</v>
       </c>
       <c r="C52">
         <v>215.66601106843655</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>9.7010606956649212</v>
+        <v>9.7580816195957123</v>
       </c>
       <c r="B53">
-        <v>-3.7728394765808693</v>
+        <v>-3.5935533991122335</v>
       </c>
       <c r="C53">
         <v>215.66601106843655</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>8.7914536853587268</v>
+        <v>8.8518046711864766</v>
       </c>
       <c r="B54">
-        <v>-3.4984110674442506</v>
+        <v>-3.3086481549517908</v>
       </c>
       <c r="C54">
         <v>215.66601106843655</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>7.8820377249333511</v>
+        <v>7.9454089822061746</v>
       </c>
       <c r="B55">
-        <v>-3.223381544707165</v>
+        <v>-3.0241166151566654</v>
       </c>
       <c r="C55">
         <v>215.66601106843655</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>6.9727750798951869</v>
+        <v>7.03886729343181</v>
       </c>
       <c r="B56">
-        <v>-2.9478696350456963</v>
+        <v>-2.740044570880988</v>
       </c>
       <c r="C56">
         <v>215.66601106843655</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>6.063582333709741</v>
+        <v>6.1321192747159188</v>
       </c>
       <c r="B57">
-        <v>-2.6721377977357736</v>
+        <v>-2.45662189521754</v>
       </c>
       <c r="C57">
         <v>215.66601106843655</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5.1543760698425256</v>
+        <v>5.2251045959110414</v>
       </c>
       <c r="B58">
-        <v>-2.3964484920533282</v>
+        <v>-2.1740384612591046</v>
       </c>
       <c r="C58">
         <v>215.66601106843655</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4.24508290572917</v>
+        <v>4.3177701843134892</v>
       </c>
       <c r="B59">
-        <v>-2.1210326066923875</v>
+        <v>-1.8924613012244826</v>
       </c>
       <c r="C59">
         <v>215.66601106843655</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3.3356695946858133</v>
+        <v>3.410091996994685</v>
       </c>
       <c r="B60">
-        <v>-1.8459947480193857</v>
+        <v>-1.6119660838365508</v>
       </c>
       <c r="C60">
         <v>215.66601106843655</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2.42611292399872</v>
+        <v>2.5020532484698217</v>
       </c>
       <c r="B61">
-        <v>-1.5714079518188548</v>
+        <v>-1.3326056369442054</v>
       </c>
       <c r="C61">
         <v>215.66601106843655</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1.5163896809541544</v>
+        <v>1.5936371532540954</v>
       </c>
       <c r="B62">
-        <v>-1.2973452538753276</v>
+        <v>-1.0544327883963423</v>
       </c>
       <c r="C62">
         <v>215.66601106843655</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.60653783386423477</v>
+        <v>0.68487120433071313</v>
       </c>
       <c r="B63">
-        <v>-1.0236871918332067</v>
+        <v>-0.77736101134078683</v>
       </c>
       <c r="C63">
         <v>215.66601106843655</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.30315992485552451</v>
+        <v>-0.22403999144508752</v>
       </c>
       <c r="B64">
-        <v>-0.74954431077636741</v>
+        <v>-0.50074636012107776</v>
       </c>
       <c r="C64">
         <v>215.66601106843655</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.212359721763735</v>
+        <v>-1.1328475487500365</v>
       </c>
       <c r="B65">
-        <v>-0.47383465764856114</v>
+        <v>-0.22380553437968975</v>
       </c>
       <c r="C65">
         <v>215.66601106843655</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.1207176834190307</v>
+        <v>-2.0413025822608861</v>
       </c>
       <c r="B66">
-        <v>-0.19547627939353204</v>
+        <v>0.054244766240910083</v>
       </c>
       <c r="C66">
         <v>215.66601106843655</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.0283341867974536</v>
+        <v>-2.9494777682066524</v>
       </c>
       <c r="B67">
-        <v>0.08521500088945673</v>
+        <v>0.33317581263998614</v>
       </c>
       <c r="C67">
         <v>215.66601106843655</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-3.9370866105447289</v>
+        <v>-3.8587320290254583</v>
       </c>
       <c r="B68">
-        <v>0.36233225547908327</v>
+        <v>0.60871075788374884</v>
       </c>
       <c r="C68">
         <v>215.66601106843655</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-4.8484290204766642</v>
+        <v>-4.7701178915268718</v>
       </c>
       <c r="B69">
-        <v>0.63130045541380186</v>
+        <v>0.87753705378554747</v>
       </c>
       <c r="C69">
         <v>215.66601106843655</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-5.7603452294196762</v>
+        <v>-5.6821760537970976</v>
       </c>
       <c r="B70">
-        <v>0.89846327139322013</v>
+        <v>1.1442474649803298</v>
       </c>
       <c r="C70">
         <v>215.66601106843655</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-6.670637028213819</v>
+        <v>-6.5933154677313075</v>
       </c>
       <c r="B71">
-        <v>1.1707370826217831</v>
+        <v>1.4138493921980904</v>
       </c>
       <c r="C71">
         <v>215.66601106843655</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-7.579848372743025</v>
+        <v>-7.5039299291838368</v>
       </c>
       <c r="B72">
-        <v>1.4464104026621192</v>
+        <v>1.6851034677273897</v>
       </c>
       <c r="C72">
         <v>215.66601106843655</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-8.4888880750094877</v>
+        <v>-8.41467732951609</v>
       </c>
       <c r="B73">
-        <v>1.7226237727569542</v>
+        <v>1.955939153491256</v>
       </c>
       <c r="C73">
         <v>215.66601106843655</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-9.3973822064445773</v>
+        <v>-9.3252870981585687</v>
       </c>
       <c r="B74">
-        <v>2.0005537105112303</v>
+        <v>2.2272079983920134</v>
       </c>
       <c r="C74">
         <v>215.66601106843655</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-10.304629133410224</v>
+        <v>-10.235251470604732</v>
       </c>
       <c r="B75">
-        <v>2.2824078149068474</v>
+        <v>2.5005080561610433</v>
       </c>
       <c r="C75">
         <v>215.66601106843655</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-11.209899142561405</v>
+        <v>-11.144042368530744</v>
       </c>
       <c r="B76">
-        <v>2.5704820340713255</v>
+        <v>2.7775013128666544</v>
       </c>
       <c r="C76">
         <v>215.66601106843655</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-12.112516573064085</v>
+        <v>-12.051170843391727</v>
       </c>
       <c r="B77">
-        <v>2.8669022469369012</v>
+        <v>3.0597266040054731</v>
       </c>
       <c r="C77">
         <v>215.66601106843655</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-13.012050053835093</v>
+        <v>-12.956324779575892</v>
       </c>
       <c r="B78">
-        <v>3.1730257065090641</v>
+        <v>3.3481662304504809</v>
       </c>
       <c r="C78">
         <v>215.66601106843655</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-13.907764606692313</v>
+        <v>-13.858972309836954</v>
       </c>
       <c r="B79">
-        <v>3.491164926040494</v>
+        <v>3.6444941028956426</v>
       </c>
       <c r="C79">
         <v>215.66601106843655</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-14.798371186841127</v>
+        <v>-14.758180532829092</v>
       </c>
       <c r="B80">
-        <v>3.8253757173135581</v>
+        <v>3.9516462801979286</v>
       </c>
       <c r="C80">
         <v>215.66601106843655</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-15.680705043133312</v>
+        <v>-15.651658882234795</v>
       </c>
       <c r="B81">
-        <v>4.1856155581823424</v>
+        <v>4.2768317106069782</v>
       </c>
       <c r="C81">
         <v>215.66601106843655</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-16.497791928699954</v>
+        <v>-16.498168440314085</v>
       </c>
       <c r="B82">
-        <v>4.7511465058761777</v>
+        <v>4.7498389191635875</v>
       </c>
       <c r="C82">
         <v>215.66601106843655</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-18.740002448224821</v>
+        <v>-18.741605118903248</v>
       </c>
       <c r="B1">
-        <v>4.5454661832095713</v>
+        <v>4.5388536161979918</v>
       </c>
       <c r="C1">
         <v>235.24828722421182</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-17.636215635175926</v>
+        <v>-17.657796011872716</v>
       </c>
       <c r="B2">
-        <v>4.5475701134081943</v>
+        <v>4.46493798065792</v>
       </c>
       <c r="C2">
         <v>235.24828722421182</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-16.570314560447063</v>
+        <v>-16.599403514765083</v>
       </c>
       <c r="B3">
-        <v>4.4049746647343682</v>
+        <v>4.2938071122709189</v>
       </c>
       <c r="C3">
         <v>235.24828722421182</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-15.510184779879797</v>
+        <v>-15.545046802397806</v>
       </c>
       <c r="B4">
-        <v>4.2403365499412313</v>
+        <v>4.1072398912608152</v>
       </c>
       <c r="C4">
         <v>235.24828722421182</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-14.454042025411876</v>
+        <v>-14.49353791905224</v>
       </c>
       <c r="B5">
-        <v>4.0604705360571263</v>
+        <v>3.9097800940065239</v>
       </c>
       <c r="C5">
         <v>235.24828722421182</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-13.401159309316366</v>
+        <v>-13.444392815173645</v>
       </c>
       <c r="B6">
-        <v>3.8681532529486149</v>
+        <v>3.7032791472056288</v>
       </c>
       <c r="C6">
         <v>235.24828722421182</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-12.35112197845752</v>
+        <v>-12.397335386946185</v>
       </c>
       <c r="B7">
-        <v>3.6649684113694239</v>
+        <v>3.48879311210423</v>
       </c>
       <c r="C7">
         <v>235.24828722421182</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-11.303686525663469</v>
+        <v>-11.352203475761046</v>
       </c>
       <c r="B8">
-        <v>3.4518460535487048</v>
+        <v>3.2669422243262742</v>
       </c>
       <c r="C8">
         <v>235.24828722421182</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-10.258471781984293</v>
+        <v>-10.308743275865645</v>
       </c>
       <c r="B9">
-        <v>3.2302420019870803</v>
+        <v>3.0386972579210876</v>
       </c>
       <c r="C9">
         <v>235.24828722421182</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-9.2150661280595756</v>
+        <v>-9.2666807104039339</v>
       </c>
       <c r="B10">
-        <v>3.0017283803496628</v>
+        <v>2.8051065212767283</v>
       </c>
       <c r="C10">
         <v>235.24828722421182</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-8.173073804665016</v>
+        <v>-8.2257522652497936</v>
       </c>
       <c r="B11">
-        <v>2.7678167366880486</v>
+        <v>2.5671779217107962</v>
       </c>
       <c r="C11">
         <v>235.24828722421182</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-7.1322837824151541</v>
+        <v>-7.1858174152945029</v>
       </c>
       <c r="B12">
-        <v>2.529313068782741</v>
+        <v>2.3254489495182642</v>
       </c>
       <c r="C12">
         <v>235.24828722421182</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-6.093208091143878</v>
+        <v>-6.1472170287690711</v>
       </c>
       <c r="B13">
-        <v>2.2842617489434067</v>
+        <v>2.0786158279740667</v>
       </c>
       <c r="C13">
         <v>235.24828722421182</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-5.0561531234615611</v>
+        <v>-5.1101550690093509</v>
       </c>
       <c r="B14">
-        <v>2.0314925526376038</v>
+        <v>1.8258984238013072</v>
       </c>
       <c r="C14">
         <v>235.24828722421182</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-4.0198796638651748</v>
+        <v>-4.0738064864308212</v>
       </c>
       <c r="B15">
-        <v>1.7757384934352911</v>
+        <v>1.5704524445358123</v>
       </c>
       <c r="C15">
         <v>235.24828722421182</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.9832511097485832</v>
+        <v>-3.0374145494568818</v>
       </c>
       <c r="B16">
-        <v>1.5213406690272284</v>
+        <v>1.3151722902036123</v>
       </c>
       <c r="C16">
         <v>235.24828722421182</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.94708691820655</v>
+        <v>-2.0015248114629172</v>
       </c>
       <c r="B17">
-        <v>1.2651692754849635</v>
+        <v>1.0579712899788167</v>
       </c>
       <c r="C17">
         <v>235.24828722421182</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.91244516950519916</v>
+        <v>-0.96684169566834033</v>
       </c>
       <c r="B18">
-        <v>1.003183120420708</v>
+        <v>0.79615511650992654</v>
       </c>
       <c r="C18">
         <v>235.24828722421182</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.12061762310488258</v>
+        <v>0.066597180283365531</v>
       </c>
       <c r="B19">
-        <v>0.7351663592285349</v>
+        <v>0.529579887194916</v>
       </c>
       <c r="C19">
         <v>235.24828722421182</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.1522953381269916</v>
+        <v>1.0989209001426987</v>
       </c>
       <c r="B20">
-        <v>0.46185948424798107</v>
+        <v>0.25873933061912768</v>
       </c>
       <c r="C20">
         <v>235.24828722421182</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.1827818540644213</v>
+        <v>2.1302585476601537</v>
       </c>
       <c r="B21">
-        <v>0.1840029878185846</v>
+        <v>-0.015872824632094489</v>
       </c>
       <c r="C21">
         <v>235.24828722421182</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.2122365474022709</v>
+        <v>3.1607162344051178</v>
       </c>
       <c r="B22">
-        <v>-0.097794413444314388</v>
+        <v>-0.29385071558346465</v>
       </c>
       <c r="C22">
         <v>235.24828722421182</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4.2406807865528195</v>
+        <v>4.1903081832224949</v>
       </c>
       <c r="B23">
-        <v>-0.38345110582215208</v>
+        <v>-0.57513994169991134</v>
       </c>
       <c r="C23">
         <v>235.24828722421182</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>5.26810143791015</v>
+        <v>5.2190256447760763</v>
       </c>
       <c r="B24">
-        <v>-0.67301725132056134</v>
+        <v>-0.85977396805641892</v>
       </c>
       <c r="C24">
         <v>235.24828722421182</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>6.2944853678683383</v>
+        <v>6.2468598697296516</v>
       </c>
       <c r="B25">
-        <v>-0.96654301194517356</v>
+        <v>-1.1477862597279716</v>
       </c>
       <c r="C25">
         <v>235.24828722421182</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>7.3198137708887847</v>
+        <v>7.2737983307905543</v>
       </c>
       <c r="B26">
-        <v>-1.2641002128701879</v>
+        <v>-1.43922473198245</v>
       </c>
       <c r="C26">
         <v>235.24828722421182</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>8.3440451537021865</v>
+        <v>8.29981338884032</v>
       </c>
       <c r="B27">
-        <v>-1.5658473319440756</v>
+        <v>-1.73419510085933</v>
       </c>
       <c r="C27">
         <v>235.24828722421182</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>9.3671323511065481</v>
+        <v>9.32487362680402</v>
       </c>
       <c r="B28">
-        <v>-1.8719645101838722</v>
+        <v>-2.0328175325909812</v>
       </c>
       <c r="C28">
         <v>235.24828722421182</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>10.389028197899886</v>
+        <v>10.348947627606735</v>
       </c>
       <c r="B29">
-        <v>-2.1826318886066138</v>
+        <v>-2.3352121934097747</v>
       </c>
       <c r="C29">
         <v>235.24828722421182</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>11.409711261623579</v>
+        <v>11.372021104443537</v>
       </c>
       <c r="B30">
-        <v>-2.4979313255470443</v>
+        <v>-2.6414337284895435</v>
       </c>
       <c r="C30">
         <v>235.24828722421182</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>12.429263040792502</v>
+        <v>12.394148291589485</v>
       </c>
       <c r="B31">
-        <v>-2.817551548610727</v>
+        <v>-2.9512746987699687</v>
       </c>
       <c r="C31">
         <v>235.24828722421182</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>13.447790766664918</v>
+        <v>13.415400553589654</v>
       </c>
       <c r="B32">
-        <v>-3.1410830027209391</v>
+        <v>-3.2644621441321995</v>
       </c>
       <c r="C32">
         <v>235.24828722421182</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>14.465401670499071</v>
+        <v>14.435849254989108</v>
       </c>
       <c r="B33">
-        <v>-3.4681161328009509</v>
+        <v>-3.5807231044573782</v>
       </c>
       <c r="C33">
         <v>235.24828722421182</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>15.482161446412595</v>
+        <v>15.455538104397993</v>
       </c>
       <c r="B34">
-        <v>-3.7984000291829139</v>
+        <v>-3.8998903999868291</v>
       </c>
       <c r="C34">
         <v>235.24828722421182</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>16.4979696399607</v>
+        <v>16.474400186686811</v>
       </c>
       <c r="B35">
-        <v>-4.1323183638344876</v>
+        <v>-4.22221997240259</v>
       </c>
       <c r="C35">
         <v>235.24828722421182</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>17.512684259557968</v>
+        <v>17.492340930791151</v>
       </c>
       <c r="B36">
-        <v>-4.4704134541322116</v>
+        <v>-4.5480735437468782</v>
       </c>
       <c r="C36">
         <v>235.24828722421182</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>18.526163313618994</v>
+        <v>18.509265765646596</v>
       </c>
       <c r="B37">
-        <v>-4.8132276174526245</v>
+        <v>-4.8778128360619073</v>
       </c>
       <c r="C37">
         <v>235.24828722421182</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>19.538162917794839</v>
+        <v>19.525012281599178</v>
       </c>
       <c r="B38">
-        <v>-5.161692336600936</v>
+        <v>-5.2120590451867175</v>
       </c>
       <c r="C38">
         <v>235.24828722421182</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>20.548031616682465</v>
+        <v>20.539146714636754</v>
       </c>
       <c r="B39">
-        <v>-5.5182957560970376</v>
+        <v>-5.5524712621476127</v>
       </c>
       <c r="C39">
         <v>235.24828722421182</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>21.555016062115303</v>
+        <v>21.551167462157618</v>
       </c>
       <c r="B40">
-        <v>-5.88591518588949</v>
+        <v>-5.9009680517677188</v>
       </c>
       <c r="C40">
         <v>235.24828722421182</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>22.558362905926774</v>
+        <v>22.560572921560059</v>
       </c>
       <c r="B41">
-        <v>-6.2674279359268583</v>
+        <v>-6.259467978870159</v>
       </c>
       <c r="C41">
         <v>235.24828722421182</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>22.558362905926774</v>
+        <v>22.560572921560059</v>
       </c>
       <c r="B42">
-        <v>-6.2674279359268583</v>
+        <v>-6.259467978870159</v>
       </c>
       <c r="C42">
         <v>235.24828722421182</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>21.519423711333335</v>
+        <v>21.527471206814475</v>
       </c>
       <c r="B43">
-        <v>-6.0218552857564971</v>
+        <v>-5.9916031517189738</v>
       </c>
       <c r="C43">
         <v>235.24828722421182</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>20.482959619873498</v>
+        <v>20.495823848397343</v>
       </c>
       <c r="B44">
-        <v>-5.7668293187983215</v>
+        <v>-5.7181756004459512</v>
       </c>
       <c r="C44">
         <v>235.24828722421182</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>19.448217567853629</v>
+        <v>19.465129527796496</v>
       </c>
       <c r="B45">
-        <v>-5.5052262584956289</v>
+        <v>-5.4411028032686479</v>
       </c>
       <c r="C45">
         <v>235.24828722421182</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>18.414444491580078</v>
+        <v>18.434886926499765</v>
       </c>
       <c r="B46">
-        <v>-5.2399223282917182</v>
+        <v>-5.1623022384046191</v>
       </c>
       <c r="C46">
         <v>235.24828722421182</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>17.380989210343337</v>
+        <v>17.40466255481833</v>
       </c>
       <c r="B47">
-        <v>-4.973404623552188</v>
+        <v>-4.8834319476290196</v>
       </c>
       <c r="C47">
         <v>235.24828722421182</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>16.347608075370538</v>
+        <v>16.374294238356804</v>
       </c>
       <c r="B48">
-        <v>-4.7066037273318253</v>
+        <v>-4.6051122269473943</v>
       </c>
       <c r="C48">
         <v>235.24828722421182</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>15.314159320872944</v>
+        <v>15.343687631543148</v>
       </c>
       <c r="B49">
-        <v>-4.4400610946077146</v>
+        <v>-4.3277039359228917</v>
       </c>
       <c r="C49">
         <v>235.24828722421182</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>14.280501181061837</v>
+        <v>14.31274838880533</v>
       </c>
       <c r="B50">
-        <v>-4.1743181803569431</v>
+        <v>-4.05156793411866</v>
       </c>
       <c r="C50">
         <v>235.24828722421182</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>13.246533416309053</v>
+        <v>13.281409809540978</v>
       </c>
       <c r="B51">
-        <v>-3.909757836084506</v>
+        <v>-3.7769593426783237</v>
       </c>
       <c r="C51">
         <v>235.24828722421182</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>12.212321891628672</v>
+        <v>12.249715773026372</v>
       </c>
       <c r="B52">
-        <v>-3.6461284994070331</v>
+        <v>-3.5037103290674287</v>
       </c>
       <c r="C52">
         <v>235.24828722421182</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>11.177973998195354</v>
+        <v>11.217737803507458</v>
       </c>
       <c r="B53">
-        <v>-3.3830200044690684</v>
+        <v>-3.2315473223320019</v>
       </c>
       <c r="C53">
         <v>235.24828722421182</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>10.143597127183728</v>
+        <v>10.185547425230164</v>
       </c>
       <c r="B54">
-        <v>-3.1200221854151464</v>
+        <v>-2.9601967515180654</v>
       </c>
       <c r="C54">
         <v>235.24828722421182</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>9.1092729263771659</v>
+        <v>9.1531990215368833</v>
       </c>
       <c r="B55">
-        <v>-2.8568231997403313</v>
+        <v>-2.6894506074021631</v>
       </c>
       <c r="C55">
         <v>235.24828722421182</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>8.0749800699939058</v>
+        <v>8.1206784121557742</v>
       </c>
       <c r="B56">
-        <v>-2.5935044983417632</v>
+        <v>-2.4193631276829146</v>
       </c>
       <c r="C56">
         <v>235.24828722421182</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>7.0406714888609025</v>
+        <v>7.0879542759114385</v>
       </c>
       <c r="B57">
-        <v>-2.3302458554671057</v>
+        <v>-2.1500541117894558</v>
       </c>
       <c r="C57">
         <v>235.24828722421182</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>6.0063001138051142</v>
+        <v>6.05499529162848</v>
       </c>
       <c r="B58">
-        <v>-2.0672270453640218</v>
+        <v>-1.8816433591509234</v>
       </c>
       <c r="C58">
         <v>235.24828722421182</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4.9718245369876568</v>
+        <v>5.0217739055037214</v>
       </c>
       <c r="B59">
-        <v>-1.8046062195911643</v>
+        <v>-1.614236259486852</v>
       </c>
       <c r="C59">
         <v>235.24828722421182</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3.9372259959063207</v>
+        <v>3.9882776332228884</v>
       </c>
       <c r="B60">
-        <v>-1.5424550389511642</v>
+        <v>-1.3478805636783795</v>
       </c>
       <c r="C60">
         <v>235.24828722421182</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2.9024913893930622</v>
+        <v>2.9544977578439284</v>
       </c>
       <c r="B61">
-        <v>-1.2808235415576439</v>
+        <v>-1.0826096128970422</v>
       </c>
       <c r="C61">
         <v>235.24828722421182</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1.8676076162798325</v>
+        <v>1.9204255624247895</v>
       </c>
       <c r="B62">
-        <v>-1.0197617655242257</v>
+        <v>-0.8184567483143772</v>
       </c>
       <c r="C62">
         <v>235.24828722421182</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.83259606639473183</v>
+        <v>0.88607529119733375</v>
       </c>
       <c r="B63">
-        <v>-0.75918801533758884</v>
+        <v>-0.55536748759300414</v>
       </c>
       <c r="C63">
         <v>235.24828722421182</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.20238390644958457</v>
+        <v>-0.14844696691094145</v>
       </c>
       <c r="B64">
-        <v>-0.49849366097663195</v>
+        <v>-0.29293605435987041</v>
       </c>
       <c r="C64">
         <v>235.24828722421182</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.2371384574443105</v>
+        <v>-1.1830121617986178</v>
       </c>
       <c r="B65">
-        <v>-0.23693833879331172</v>
+        <v>-0.030668848733008326</v>
       </c>
       <c r="C65">
         <v>235.24828722421182</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.271473741780643</v>
+        <v>-2.2174912433642797</v>
       </c>
       <c r="B66">
-        <v>0.026218314860415572</v>
+        <v>0.23192772916955073</v>
       </c>
       <c r="C66">
         <v>235.24828722421182</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.3054463152566047</v>
+        <v>-3.2519218717415073</v>
       </c>
       <c r="B67">
-        <v>0.29076029287452765</v>
+        <v>0.49470963422668429</v>
       </c>
       <c r="C67">
         <v>235.24828722421182</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-4.3401143360975194</v>
+        <v>-4.287008548003846</v>
       </c>
       <c r="B68">
-        <v>0.55264610510673762</v>
+        <v>0.7549822413049051</v>
       </c>
       <c r="C68">
         <v>235.24828722421182</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-5.3762973521219175</v>
+        <v>-5.3232969161281787</v>
       </c>
       <c r="B69">
-        <v>0.80874560112168614</v>
+        <v>1.0106585330394264</v>
       </c>
       <c r="C69">
         <v>235.24828722421182</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-6.4128588670937887</v>
+        <v>-6.3600303507646752</v>
       </c>
       <c r="B70">
-        <v>1.0633994723439775</v>
+        <v>1.264632503152616</v>
       </c>
       <c r="C70">
         <v>235.24828722421182</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-7.4485597815182709</v>
+        <v>-7.3963839181806392</v>
       </c>
       <c r="B71">
-        <v>1.3213402892663351</v>
+        <v>1.520059416062159</v>
       </c>
       <c r="C71">
         <v>235.24828722421182</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-8.4837066269195667</v>
+        <v>-8.4325617204385388</v>
       </c>
       <c r="B72">
-        <v>1.5813972967939818</v>
+        <v>1.7761586078798433</v>
       </c>
       <c r="C72">
         <v>235.24828722421182</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-9.5188115830351787</v>
+        <v>-9.468904775470973</v>
       </c>
       <c r="B73">
-        <v>1.8416142947002905</v>
+        <v>2.0316257292914526</v>
       </c>
       <c r="C73">
         <v>235.24828722421182</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-10.553663791436717</v>
+        <v>-10.505272728895884</v>
       </c>
       <c r="B74">
-        <v>2.1027966278187415</v>
+        <v>2.2869976175846554</v>
       </c>
       <c r="C74">
         <v>235.24828722421182</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-11.587867674460943</v>
+        <v>-11.541402247903536</v>
       </c>
       <c r="B75">
-        <v>2.3664551507533016</v>
+        <v>2.5432814865654048</v>
       </c>
       <c r="C75">
         <v>235.24828722421182</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-12.621011815671166</v>
+        <v>-12.577019458288119</v>
       </c>
       <c r="B76">
-        <v>2.6341612121298</v>
+        <v>2.8015248695109207</v>
       </c>
       <c r="C76">
         <v>235.24828722421182</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-13.652715259925104</v>
+        <v>-13.611870767816551</v>
       </c>
       <c r="B77">
-        <v>2.9073698178399092</v>
+        <v>3.0626977237861905</v>
       </c>
       <c r="C77">
         <v>235.24828722421182</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-14.682734736031613</v>
+        <v>-14.645794253542698</v>
       </c>
       <c r="B78">
-        <v>3.18701010881682</v>
+        <v>3.3274193836359918</v>
       </c>
       <c r="C78">
         <v>235.24828722421182</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-15.710655836848588</v>
+        <v>-15.678514057312846</v>
       </c>
       <c r="B79">
-        <v>3.4746648562752611</v>
+        <v>3.5967449706806889</v>
       </c>
       <c r="C79">
         <v>235.24828722421182</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-16.735751840469849</v>
+        <v>-16.709546395034781</v>
       </c>
       <c r="B80">
-        <v>3.7731096748158488</v>
+        <v>3.8725248962581937</v>
       </c>
       <c r="C80">
         <v>235.24828722421182</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-17.756238759898338</v>
+        <v>-17.737703591676219</v>
       </c>
       <c r="B81">
-        <v>4.089158257977112</v>
+        <v>4.1593018631584915</v>
       </c>
       <c r="C81">
         <v>235.24828722421182</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-18.740002448224821</v>
+        <v>-18.741605118903248</v>
       </c>
       <c r="B82">
-        <v>4.5454661832095713</v>
+        <v>4.5388536161979918</v>
       </c>
       <c r="C82">
         <v>235.24828722421182</v>
